--- a/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино ЗПФ\ostankino_zpf\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9126860-A0EA-4AA4-BDC8-1CDDDF9670E7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737CB7B6-D5AA-419F-8BF5-DF64C4C4EF41}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>1С</t>
   </si>
@@ -70,6 +70,39 @@
   </si>
   <si>
     <t>7216 СОЧНЫЕ СО СЛ.МАСЛ.ПМ пельм пл.0.7кг зам. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>БЛИНЧ.КРУГЛЫЕ С САД.ЯБЛОК.1/420 зам_ПОСТ</t>
+  </si>
+  <si>
+    <t>БЛИНЧ.КРУГЛЫЕ С МЯСОМ 4.5кг зам_ФМ</t>
+  </si>
+  <si>
+    <t>БЛИНЧ.КРУГЛЫЕ С ТВОРОГОМ 4.5кг зам_ФМ</t>
+  </si>
+  <si>
+    <t>БЛИНЧ.КРУГЛЫЕ С ГРУШЕЙ пл.1/420 зам.</t>
+  </si>
+  <si>
+    <t>БЛИНЧ.КРУГЛЫЕ С ВЕТЧ.И СЫР.ПМ 1/300 зам.</t>
+  </si>
+  <si>
+    <t>БЛИНЧ.КРУГЛЫЕ С ПЕЧЕНЬЮ ПМ 1/300 зам.</t>
+  </si>
+  <si>
+    <t>БЛИНЧ.С МЯСОМ пл.1/350 зам.</t>
+  </si>
+  <si>
+    <t>БЛИНЧ.КРУГЛЫЕ С ТВОРОГОМ ПМ 1/300 зам.</t>
+  </si>
+  <si>
+    <t>БЛИНЧ.С КУРИНЫМ МЯСОМ пл.1/350 зам.</t>
+  </si>
+  <si>
+    <t>БЛИНЧ.КРУГЛЫЕ С САД.ЯБЛОК.пл.1/300 зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ СО СЛ.МАСЛ.ПМ пельм пл.0.7кг зам.</t>
   </si>
 </sst>
 </file>
@@ -446,55 +479,121 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="B2" s="3">
+        <v>1002134275579</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="B3" s="3">
+        <v>1002131155754</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="B4" s="3">
+        <v>1002131185755</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="B5" s="3">
+        <v>1002134615897</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="B6" s="3">
+        <v>1002133376148</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="B7" s="3">
+        <v>1002131166149</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="B8" s="3">
+        <v>1002131156168</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="B9" s="3">
+        <v>1002131186202</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="B10" s="3">
+        <v>1002131146209</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="B11" s="3">
+        <v>1002134276819</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1002116437216</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
